--- a/Docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/Docs/Lab01/Lab01_ReviewReport.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UBB INFO\UBB INFO - ANUL III (2025-2026)\Semestrul 6\VVSS\Lab\Docs\Lab01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VVSS\Docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB05E904-B6B0-4373-B2FD-D0F38ACA27B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AA400D-ADFF-4258-A3AA-F9D6DBCF96C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" tabRatio="650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -18,25 +18,12 @@
     <sheet name="Coding Phase Defects" sheetId="5" r:id="rId3"/>
     <sheet name="Tool-basedCodeAnalysis" sheetId="8" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="70">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -195,19 +182,77 @@
   </si>
   <si>
     <t>In document nu se specifica daca aplicatia porneste cu o baza de date prepopulata sau daca utilizatorul trebuie sa o configureze de la zero. De asemenea, nu se specifica cum se comporta sistemul la prima rulare cand fisierele .csv sau .txt nu exista pe disc.</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>Partitionarea pe pachete lipseste din diagrama de clase</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>Controller-ul contine liste de produse, retete, comanda curenta, produsele din comanda, ar trebui ca repo-ul sa tina aceste liste</t>
+  </si>
+  <si>
+    <t>Tipul si categoria baututilor sunt de tip enum, dar in cerinta 3 se specifica ca user-ul poate modifica/sterge/adauga tipuri sau categorii de bauturi.</t>
+  </si>
+  <si>
+    <t>Lipseste gestionarea rolurilor de Admin/User</t>
+  </si>
+  <si>
+    <t>DailyRaportService are o relatie numita "repo" spre interfata Repository si nu este clar din arhitectura ce fel de date se extrag pentru raporturi</t>
+  </si>
+  <si>
+    <t>Nu, datorita DrinkShopController care detine liste de produse, comenzi, etc, incalcand principiul singurei reposnsabiliati</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>Clasa Stoc este izolata</t>
+  </si>
+  <si>
+    <t>ProducTest nu ar trebui sa apara in diagrama</t>
+  </si>
+  <si>
+    <t>Chiar daca avem clase de validare, arhitectura nu include clar o componenta pentru tratarea erorilor, spre exeplu: ErrorHandler</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -393,91 +438,92 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -786,37 +832,37 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J27"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="7" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
+    <col min="6" max="7" width="8.88671875" style="6"/>
     <col min="8" max="8" width="10" style="6" customWidth="1"/>
     <col min="9" max="9" width="21" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" style="6" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="6"/>
+    <col min="10" max="10" width="12.109375" style="6" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -825,65 +871,65 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="35">
+      <c r="J3" s="21">
         <v>235</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="24"/>
+      <c r="E4" s="29"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="21">
         <v>235</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="25" t="s">
+      <c r="D5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="26"/>
+      <c r="E5" s="31"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -897,222 +943,222 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="36" t="s">
+      <c r="C10" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="36">
+      <c r="D10" s="22">
         <v>1</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="23" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C11" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="22">
         <v>1</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="23" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B25" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C12" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="22">
         <v>1</v>
       </c>
-      <c r="E12" s="37" t="s">
+      <c r="E12" s="23" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C13" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="36">
+      <c r="D13" s="22">
         <v>1</v>
       </c>
-      <c r="E13" s="37" t="s">
+      <c r="E13" s="23" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C14" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="22">
         <v>1</v>
       </c>
-      <c r="E14" s="37" t="s">
+      <c r="E14" s="23" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="22">
         <v>1</v>
       </c>
-      <c r="E15" s="37" t="s">
+      <c r="E15" s="23" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C16" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="36">
+      <c r="D16" s="22">
         <v>1</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E16" s="23" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C17" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="22">
         <v>1</v>
       </c>
-      <c r="E17" s="37" t="s">
+      <c r="E17" s="23" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" ht="72" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C18" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="D18" s="36">
+      <c r="D18" s="22">
         <v>1</v>
       </c>
-      <c r="E18" s="37" t="s">
+      <c r="E18" s="23" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C19" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="22">
         <v>1</v>
       </c>
-      <c r="E19" s="37" t="s">
+      <c r="E19" s="23" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="36" t="s">
+      <c r="C20" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="22">
         <v>1</v>
       </c>
-      <c r="E20" s="37" t="s">
+      <c r="E20" s="23" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C21" s="38"/>
-      <c r="D21" s="38"/>
-      <c r="E21" s="39"/>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="25"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="37"/>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="23"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C23" s="38"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="39"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="25"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="C24" s="38"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="39"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24" s="25"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="39"/>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="25"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C27" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -1135,35 +1181,35 @@
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="4" width="16.28515625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="22.140625" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
+    <col min="3" max="4" width="16.33203125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="6"/>
+    <col min="9" max="9" width="22.109375" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -1172,57 +1218,65 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I3" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="16">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="27"/>
+      <c r="E4" s="32"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I4" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="34"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1236,96 +1290,136 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E10" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E11" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B26" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>53</v>
+      </c>
       <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="D13" s="1"/>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E13" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
+      </c>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E14" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E15" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>58</v>
+      </c>
       <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="D18" s="1"/>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E18" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1334,7 +1428,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1343,7 +1437,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1352,7 +1446,7 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1361,7 +1455,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1370,7 +1464,7 @@
       <c r="D24" s="1"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1379,7 +1473,7 @@
       <c r="D25" s="1"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1388,12 +1482,14 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C28" s="11" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="12"/>
-      <c r="E28" s="1"/>
+      <c r="E28" s="1">
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1415,36 +1511,36 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.42578125" style="6" customWidth="1"/>
-    <col min="6" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="6"/>
+    <col min="9" max="9" width="26.6640625" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -1453,57 +1549,65 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I3" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="16">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="30"/>
+      <c r="E4" s="35"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I4" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="32"/>
+      <c r="E5" s="37"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1517,7 +1621,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1525,7 +1629,7 @@
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1534,7 +1638,7 @@
       <c r="D11" s="1"/>
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -1543,7 +1647,7 @@
       <c r="D12" s="1"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1552,7 +1656,7 @@
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1561,7 +1665,7 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1570,7 +1674,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1579,7 +1683,7 @@
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1588,7 +1692,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1597,7 +1701,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1606,7 +1710,7 @@
       <c r="D19" s="1"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1615,7 +1719,7 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1624,7 +1728,7 @@
       <c r="D21" s="1"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1633,7 +1737,7 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1642,7 +1746,7 @@
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1651,7 +1755,7 @@
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1660,7 +1764,7 @@
       <c r="D25" s="2"/>
       <c r="E25" s="2"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1669,7 +1773,7 @@
       <c r="D26" s="1"/>
       <c r="E26" s="2"/>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1678,7 +1782,7 @@
       <c r="D27" s="2"/>
       <c r="E27" s="1"/>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1687,7 +1791,7 @@
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1696,7 +1800,7 @@
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1705,7 +1809,7 @@
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="C32" s="11" t="s">
         <v>8</v>
       </c>
@@ -1732,37 +1836,37 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" style="6"/>
-    <col min="2" max="2" width="12.28515625" style="6" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" style="6" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="6"/>
+    <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="23.85546875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="16.5703125" style="6" customWidth="1"/>
-    <col min="7" max="8" width="8.85546875" style="6"/>
-    <col min="9" max="9" width="26.7109375" style="6" customWidth="1"/>
-    <col min="10" max="16384" width="8.85546875" style="6"/>
+    <col min="5" max="5" width="23.88671875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5546875" style="6" customWidth="1"/>
+    <col min="7" max="8" width="8.88671875" style="6"/>
+    <col min="9" max="9" width="26.6640625" style="6" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="4"/>
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="23" t="s">
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -1771,47 +1875,47 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
       <c r="I3" s="16"/>
       <c r="J3" s="16"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="35"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="8"/>
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="21"/>
-      <c r="E6" s="21"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
       <c r="F6" s="19"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
         <v>4</v>
       </c>
@@ -1828,7 +1932,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
@@ -1837,7 +1941,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
@@ -1847,7 +1951,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
@@ -1857,7 +1961,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1867,7 +1971,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1877,7 +1981,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1887,7 +1991,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1897,7 +2001,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1907,7 +2011,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1917,7 +2021,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1927,7 +2031,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1937,7 +2041,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1947,7 +2051,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="3">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1957,7 +2061,7 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="3">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1967,7 +2071,7 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="3">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1977,7 +2081,7 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="3">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1987,7 +2091,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="3">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1997,7 +2101,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="3">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2007,7 +2111,7 @@
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="3">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2017,7 +2121,7 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="3">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2027,7 +2131,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="3">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2037,15 +2141,15 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="C32" s="33" t="s">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C32" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="39"/>
       <c r="F32" s="17"/>
     </row>
-    <row r="35" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="6:6" x14ac:dyDescent="0.3">
       <c r="F35" s="20"/>
     </row>
   </sheetData>

--- a/Docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/Docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VVSS\Docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AA400D-ADFF-4258-A3AA-F9D6DBCF96C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54708136-BCDC-4DA9-8170-65B7BBD871AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="528" yWindow="1476" windowWidth="17280" windowHeight="8880" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="88">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -190,15 +190,6 @@
     <t>A03</t>
   </si>
   <si>
-    <t>A04</t>
-  </si>
-  <si>
-    <t>A05</t>
-  </si>
-  <si>
-    <t>A08</t>
-  </si>
-  <si>
     <t>A09</t>
   </si>
   <si>
@@ -208,21 +199,12 @@
     <t>A01</t>
   </si>
   <si>
-    <t>Controller-ul contine liste de produse, retete, comanda curenta, produsele din comanda, ar trebui ca repo-ul sa tina aceste liste</t>
-  </si>
-  <si>
     <t>Tipul si categoria baututilor sunt de tip enum, dar in cerinta 3 se specifica ca user-ul poate modifica/sterge/adauga tipuri sau categorii de bauturi.</t>
   </si>
   <si>
-    <t>Lipseste gestionarea rolurilor de Admin/User</t>
-  </si>
-  <si>
     <t>DailyRaportService are o relatie numita "repo" spre interfata Repository si nu este clar din arhitectura ce fel de date se extrag pentru raporturi</t>
   </si>
   <si>
-    <t>Nu, datorita DrinkShopController care detine liste de produse, comenzi, etc, incalcand principiul singurei reposnsabiliati</t>
-  </si>
-  <si>
     <t>A10</t>
   </si>
   <si>
@@ -232,7 +214,82 @@
     <t>ProducTest nu ar trebui sa apara in diagrama</t>
   </si>
   <si>
-    <t>Chiar daca avem clase de validare, arhitectura nu include clar o componenta pentru tratarea erorilor, spre exeplu: ErrorHandler</t>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>DrinkShopContoller line169</t>
+  </si>
+  <si>
+    <t>CsvExporter</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>DrinkShopContoller</t>
+  </si>
+  <si>
+    <t>DrinkShopController - onAddProduct</t>
+  </si>
+  <si>
+    <t>DailyReportService</t>
+  </si>
+  <si>
+    <t>StocService</t>
+  </si>
+  <si>
+    <t>OrderService</t>
+  </si>
+  <si>
+    <t>niciun validator nu este folosit!</t>
+  </si>
+  <si>
+    <t>Validatorii nu sunt legati de clase</t>
+  </si>
+  <si>
+    <t>nu avem validari pentru adaugarea unui element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">din O(NxMxP) -&gt; O(P + (NxM)); N - nr de comenzi, M - nr de produse pe comanda, P - nr total de produse
+</t>
+  </si>
+  <si>
+    <t>Eroare afisata doar in consola</t>
+  </si>
+  <si>
+    <t>Utilizatorul nu este informat de crearea csv-ului</t>
+  </si>
+  <si>
+    <t xml:space="preserve">showError nu este folosit in functia onAddProduct() </t>
+  </si>
+  <si>
+    <t>lipsesc validatorii pnetru onAddProduct</t>
+  </si>
+  <si>
+    <t>Numele "repo" este prea vag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metoda neutilizata public void update(Stoc s)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">comentarii in functia public List&lt;Order&gt; getAllOrders() {
+</t>
+  </si>
+  <si>
+    <t>CsvExporter este izolvat</t>
+  </si>
+  <si>
+    <t>ReceiptGenerator este izolat</t>
+  </si>
+  <si>
+    <t>DrinkShopApp este izolat</t>
   </si>
 </sst>
 </file>
@@ -481,6 +538,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -523,7 +581,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -850,19 +907,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -886,10 +943,10 @@
       <c r="C4" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="29"/>
+      <c r="E4" s="30"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
@@ -904,10 +961,10 @@
       <c r="C5" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="31"/>
+      <c r="E5" s="32"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
@@ -919,15 +976,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1180,7 +1237,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="6"/>
@@ -1197,19 +1254,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -1222,7 +1279,7 @@
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="26" t="s">
         <v>34</v>
       </c>
       <c r="J3" s="16">
@@ -1233,14 +1290,14 @@
       <c r="C4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="33"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="26" t="s">
         <v>33</v>
       </c>
       <c r="J4" s="3">
@@ -1251,10 +1308,10 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="34"/>
+      <c r="E5" s="35"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
@@ -1266,15 +1323,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1295,11 +1352,11 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -1312,85 +1369,85 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
-        <f t="shared" ref="B12:B26" si="0">B11+1</f>
+        <f>B11+1</f>
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
-        <f t="shared" si="0"/>
+        <f>B12+1</f>
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D13" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
-        <f t="shared" si="0"/>
+        <f>B13+1</f>
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="B15:B22" si="0">B14+1</f>
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D15" s="1"/>
+        <v>53</v>
+      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="D16" s="1"/>
       <c r="E16" s="2" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D17" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="D17" s="1"/>
       <c r="E17" s="2" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
@@ -1399,25 +1456,21 @@
         <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="2"/>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
@@ -1446,48 +1499,12 @@
       <c r="D22" s="1"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="3">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="2"/>
-    </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="3">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="2"/>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="3">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="3">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="2"/>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="C28" s="11" t="s">
+      <c r="C24" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="12"/>
-      <c r="E28" s="1">
+      <c r="D24" s="12"/>
+      <c r="E24" s="1">
         <v>0.5</v>
       </c>
     </row>
@@ -1517,7 +1534,7 @@
     <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
     <col min="3" max="3" width="16.33203125" style="6" customWidth="1"/>
     <col min="4" max="4" width="18" style="6" customWidth="1"/>
-    <col min="5" max="5" width="41.44140625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="62.44140625" style="6" customWidth="1"/>
     <col min="6" max="8" width="8.88671875" style="6"/>
     <col min="9" max="9" width="26.6640625" style="6" customWidth="1"/>
     <col min="10" max="16384" width="8.88671875" style="6"/>
@@ -1528,19 +1545,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -1553,7 +1570,7 @@
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="40" t="s">
+      <c r="I3" s="26" t="s">
         <v>34</v>
       </c>
       <c r="J3" s="16">
@@ -1564,14 +1581,14 @@
       <c r="C4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="35"/>
+      <c r="E4" s="36"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="40" t="s">
+      <c r="I4" s="26" t="s">
         <v>33</v>
       </c>
       <c r="J4" s="3">
@@ -1582,10 +1599,10 @@
       <c r="C5" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="36" t="s">
+      <c r="D5" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="37"/>
+      <c r="E5" s="38"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
@@ -1597,15 +1614,15 @@
       <c r="C6" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="10" t="s">
@@ -1621,94 +1638,152 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
+      <c r="C12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="C13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
+      <c r="C15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="C18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="D19" s="1"/>
-      <c r="E19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
@@ -1814,7 +1889,9 @@
         <v>8</v>
       </c>
       <c r="D32" s="12"/>
-      <c r="E32" s="1"/>
+      <c r="E32" s="1">
+        <v>0.5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1854,19 +1931,19 @@
       <c r="B1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="27" t="s">
+      <c r="H1" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
       <c r="H2" s="3"/>
       <c r="I2" s="18" t="s">
         <v>30</v>
@@ -1886,8 +1963,8 @@
       <c r="C4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="35"/>
-      <c r="E4" s="35"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
@@ -1898,8 +1975,8 @@
       <c r="C5" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
       <c r="H5" s="16" t="s">
         <v>22</v>
       </c>
@@ -1911,8 +1988,8 @@
       <c r="C6" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
       <c r="F6" s="19"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -2142,11 +2219,11 @@
       <c r="F30" s="2"/>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="D32" s="39"/>
-      <c r="E32" s="39"/>
+      <c r="D32" s="40"/>
+      <c r="E32" s="40"/>
       <c r="F32" s="17"/>
     </row>
     <row r="35" spans="6:6" x14ac:dyDescent="0.3">

--- a/Docs/Lab01/Lab01_ReviewReport.xlsx
+++ b/Docs/Lab01/Lab01_ReviewReport.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VVSS\Docs\Lab01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54708136-BCDC-4DA9-8170-65B7BBD871AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A44C96-294B-4796-8B6B-C3305D402F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="528" yWindow="1476" windowWidth="17280" windowHeight="8880" tabRatio="650" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="650" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Requirements Phase Defects" sheetId="7" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="130">
   <si>
     <t>Document  Title:</t>
   </si>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>Tool-based Code Analysis</t>
-  </si>
-  <si>
-    <t>Effort to perform tool-based code analysis (hours):</t>
   </si>
   <si>
     <t>Negru Diana-Maria</t>
@@ -290,19 +287,177 @@
   </si>
   <si>
     <t>DrinkShopApp este izolat</t>
+  </si>
+  <si>
+    <t>Replace this usage of 'Stream.collect(Collectors.toList())' with 'Stream.toList()' and ensure that the list is unmodified.</t>
+  </si>
+  <si>
+    <t>return getAllProducts().stream()
+                .filter(p -&gt; p.getTip() == tip)
+                .collect(Collectors.toList());</t>
+  </si>
+  <si>
+    <t>return getAllProducts().stream()
+                .filter(p -&gt; p.getTip() == tip)
+                .toList();</t>
+  </si>
+  <si>
+    <t>ProductService, 52</t>
+  </si>
+  <si>
+    <t>return getAllProducts().stream()
+                .filter(p -&gt; p.getCategorie() == categorie)
+                .collect(Collectors.toList());
+    }</t>
+  </si>
+  <si>
+    <t>return getAllProducts().stream()
+                .filter(p -&gt; p.getCategorie() == categorie)
+                .toList();</t>
+  </si>
+  <si>
+    <t>ProductService, 8</t>
+  </si>
+  <si>
+    <t>Remove this unused import 'java.util.stream.Collectors'.</t>
+  </si>
+  <si>
+    <t>import java.util.stream.Collectors;</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>ProductService, 34</t>
+  </si>
+  <si>
+    <t>This block of commented-out lines of code should be removed.</t>
+  </si>
+  <si>
+    <t>public List&lt;Product&gt; getAllProducts() {
+//        Iterable&lt;Product&gt; it=productRepo.findAll();
+//        ArrayList&lt;Product&gt; products=new ArrayList&lt;&gt;();
+//        it.forEach(products::add);
+//        return products;
+//        return StreamSupport.stream(productRepo.findAll().spliterator(), false)
+//                    .collect(Collectors.toList());
+        return productRepo.findAll();
+    }</t>
+  </si>
+  <si>
+    <t>public List&lt;Product&gt; getAllProducts() {
+        return productRepo.findAll();
+    }</t>
+  </si>
+  <si>
+    <t>ReceiptGenerator, 9</t>
+  </si>
+  <si>
+    <t>Add a private constructor to hide the implicit public one.</t>
+  </si>
+  <si>
+    <t>private ReceiptGenerator(){}</t>
+  </si>
+  <si>
+    <t>ReceiptGenerator, 17</t>
+  </si>
+  <si>
+    <t>Remove the parentheses around the "p1" parameter</t>
+  </si>
+  <si>
+    <t>Product p = products.stream().filter((p1)-&gt;i.getProduct().getId()==p1.getId()).toList().get(0);</t>
+  </si>
+  <si>
+    <t>Product p = products.stream().filter(p1-&gt;i.getProduct().getId()==p1.getId()).toList().get(0);</t>
+  </si>
+  <si>
+    <t>ReceiptGenerator, 18</t>
+  </si>
+  <si>
+    <t>Use multiple calls to "append" instead of string concatenation.</t>
+  </si>
+  <si>
+    <t>sb.append(p.getNume()+": ").append(p.getPret()).append(" x ").append(i.getQuantity()).append(" = ").append(i.getTotal()).append(" RON\n");</t>
+  </si>
+  <si>
+    <t>sb.append(p.getNume()).append(": ").append(p.getPret()).append(" x ").append(i.getQuantity()).append(" = ").append(i.getTotal()).append(" RON\n");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    @FXML private TextField txtProdName, txtProdPrice;</t>
+  </si>
+  <si>
+    <t>Declare "txtProdPrice" on a separate line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    @FXML private TextField txtProdName;
+    @FXML private TextField txtProdPrice;</t>
+  </si>
+  <si>
+    <t>DrinkShopController, 27</t>
+  </si>
+  <si>
+    <t>DrinkShopController, 40</t>
+  </si>
+  <si>
+    <t>Declare "txtNewIngredCant" on a separate line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    @FXML private TextField txtNewIngredName, txtNewIngredCant;
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    @FXML private TextField txtNewIngredName;
+    @FXML private TextField txtNewIngredCant;</t>
+  </si>
+  <si>
+    <t>DrinkShopController, 123</t>
+  </si>
+  <si>
+    <t>Use isEmpty() to check whether the collection is empty or not.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> if (service.getAllProducts().stream().filter(p-&gt;p.getId()==r.getId()).toList().size()&gt;0) {</t>
+  </si>
+  <si>
+    <t>if (!service.getAllProducts().stream().filter(p-&gt;p.getId()==r.getId()).toList().isEmpty()) {</t>
+  </si>
+  <si>
+    <t>DrinkShopController, 12</t>
+  </si>
+  <si>
+    <t>Remove this unused import 'java.net.SocketOption'.</t>
+  </si>
+  <si>
+    <t>import java.net.SocketOption;</t>
+  </si>
+  <si>
+    <t>ProductService, 45</t>
+  </si>
+  <si>
+    <t>Effort to perform tool-based code analysis (hours): 0.5</t>
+  </si>
+  <si>
+    <t>SonarQube for IDE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -495,92 +650,96 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -933,7 +1092,7 @@
         <v>20</v>
       </c>
       <c r="I3" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J3" s="21">
         <v>235</v>
@@ -951,7 +1110,7 @@
         <v>21</v>
       </c>
       <c r="I4" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J4" s="21">
         <v>235</v>
@@ -1005,13 +1164,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" s="22">
         <v>1</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -1020,13 +1179,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" s="22">
         <v>1</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
@@ -1035,13 +1194,13 @@
         <v>3</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="22">
         <v>1</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1050,13 +1209,13 @@
         <v>4</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="22">
         <v>1</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1065,13 +1224,13 @@
         <v>5</v>
       </c>
       <c r="C14" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="22">
         <v>1</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1080,13 +1239,13 @@
         <v>6</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="22">
         <v>1</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
@@ -1095,13 +1254,13 @@
         <v>7</v>
       </c>
       <c r="C16" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D16" s="22">
         <v>1</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -1110,13 +1269,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" s="22">
         <v>1</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="72" x14ac:dyDescent="0.3">
@@ -1125,13 +1284,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D18" s="22">
         <v>1</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="92.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1140,13 +1299,13 @@
         <v>10</v>
       </c>
       <c r="C19" s="22" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D19" s="22">
         <v>1</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="2:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -1155,13 +1314,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D20" s="22">
         <v>1</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
@@ -1280,7 +1439,7 @@
         <v>20</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J3" s="16">
         <v>235</v>
@@ -1298,7 +1457,7 @@
         <v>21</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" s="3">
         <v>235</v>
@@ -1352,11 +1511,11 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -1365,11 +1524,11 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1378,11 +1537,11 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
@@ -1391,11 +1550,11 @@
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1404,11 +1563,11 @@
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -1417,11 +1576,11 @@
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1430,11 +1589,11 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
@@ -1443,11 +1602,11 @@
         <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
@@ -1456,11 +1615,11 @@
         <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -1571,7 +1730,7 @@
         <v>20</v>
       </c>
       <c r="I3" s="26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J3" s="16">
         <v>235</v>
@@ -1589,7 +1748,7 @@
         <v>21</v>
       </c>
       <c r="I4" s="26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J4" s="3">
         <v>235</v>
@@ -1643,13 +1802,13 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1658,13 +1817,13 @@
         <v>2</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -1673,13 +1832,13 @@
         <v>3</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1688,13 +1847,13 @@
         <v>4</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -1703,13 +1862,13 @@
         <v>5</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
@@ -1718,13 +1877,13 @@
         <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -1733,13 +1892,13 @@
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1748,13 +1907,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18" spans="2:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -1763,13 +1922,13 @@
         <v>9</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
@@ -1778,11 +1937,11 @@
         <v>10</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
@@ -1918,7 +2077,7 @@
     <col min="1" max="1" width="8.88671875" style="6"/>
     <col min="2" max="2" width="12.33203125" style="6" customWidth="1"/>
     <col min="3" max="3" width="16.33203125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="18" style="6" customWidth="1"/>
+    <col min="4" max="4" width="26.88671875" style="6" customWidth="1"/>
     <col min="5" max="5" width="23.88671875" style="6" customWidth="1"/>
     <col min="6" max="6" width="16.5546875" style="6" customWidth="1"/>
     <col min="7" max="8" width="8.88671875" style="6"/>
@@ -1956,20 +2115,30 @@
       <c r="H3" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
+      <c r="I3" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" s="16">
+        <v>235</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C4" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="36"/>
+      <c r="D4" s="36" t="s">
+        <v>129</v>
+      </c>
       <c r="E4" s="36"/>
       <c r="H4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="42" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" s="3">
+        <v>235</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
@@ -2009,114 +2178,202 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>1</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B11" s="3">
         <f>B10+1</f>
         <v>2</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C11" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <f t="shared" ref="B12:B30" si="0">B11+1</f>
         <v>3</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="288" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>98</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B15" s="3">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C15" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="B16" s="3">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" ht="86.4" x14ac:dyDescent="0.3">
       <c r="B17" s="3">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="B18" s="3">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C18" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="100.8" x14ac:dyDescent="0.3">
       <c r="B19" s="3">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="C19" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="B20" s="3">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
+      <c r="C20" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="3">
@@ -2220,7 +2477,7 @@
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="C32" s="39" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="D32" s="40"/>
       <c r="E32" s="40"/>
